--- a/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
@@ -13208,12 +13208,16 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="inlineStr">
         <is>
@@ -13314,12 +13318,16 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="inlineStr">
         <is>
@@ -13420,12 +13428,16 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr">
         <is>
@@ -13526,12 +13538,16 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr">
         <is>
@@ -13632,12 +13648,16 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr">
         <is>
@@ -72877,7 +72897,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -72885,7 +72905,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
@@ -72944,7 +72968,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -72952,7 +72976,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
@@ -73011,7 +73039,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -73019,7 +73047,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
@@ -73078,7 +73110,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -73086,7 +73118,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
@@ -73145,7 +73181,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -73153,7 +73189,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
@@ -73295,19 +73335,19 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1535</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>4413</v>
+        <v>5948</v>
       </c>
       <c r="O101" t="n">
         <v>1482</v>
       </c>
       <c r="P101" t="n">
-        <v>1</v>
+        <v>0.7419</v>
       </c>
       <c r="Q101" t="n">
         <v>0.6215000000000001</v>
@@ -73362,19 +73402,19 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4073</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1875</v>
+        <v>5948</v>
       </c>
       <c r="O102" t="n">
         <v>1482</v>
       </c>
       <c r="P102" t="n">
-        <v>1</v>
+        <v>0.3152</v>
       </c>
       <c r="Q102" t="n">
         <v>0.2476</v>
@@ -73429,19 +73469,19 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2658</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3290</v>
+        <v>5948</v>
       </c>
       <c r="O103" t="n">
         <v>1482</v>
       </c>
       <c r="P103" t="n">
-        <v>1</v>
+        <v>0.5531</v>
       </c>
       <c r="Q103" t="n">
         <v>0.3313</v>
@@ -73496,19 +73536,19 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1478</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4470</v>
+        <v>5948</v>
       </c>
       <c r="O104" t="n">
         <v>1482</v>
       </c>
       <c r="P104" t="n">
-        <v>1</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="Q104" t="n">
         <v>0.5655</v>
@@ -73567,19 +73607,19 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1271</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>1113</v>
       </c>
       <c r="N105" t="n">
-        <v>4677</v>
+        <v>5948</v>
       </c>
       <c r="O105" t="n">
         <v>369</v>
       </c>
       <c r="P105" t="n">
-        <v>1</v>
+        <v>0.7863</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -73638,19 +73678,19 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1320</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
         <v>961</v>
       </c>
       <c r="N106" t="n">
-        <v>4628</v>
+        <v>5948</v>
       </c>
       <c r="O106" t="n">
         <v>521</v>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>0.7781</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -82005,7 +82045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82111,7 +82151,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PR_TALK_06</t>
+          <t>PR_EDU_COST_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -82121,7 +82161,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>가정 내 대화</t>
+          <t>교육비·사교육비</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -82131,7 +82171,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자녀와 대화 시간 및 주제 - 5)학교생활</t>
+          <t>교육비 및 사교육 - 1)학교에 낸 돈(체험활동비, 방과 후 학교 수강료 포함)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -82141,17 +82181,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2주기 PRQ3_2_5에 1(해당) 코드가 없고 0/결측만 존재 — 결측이 '해당'일 가능성. 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>대화 주제(학교생활)·복수응답 동일</t>
+          <t>양 주기 모두 이상치 확인 필요(2주기 코드북에 이상치 주의 명시)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -82163,7 +82203,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PR_TALK_07</t>
+          <t>PR_EDU_COST_02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -82173,7 +82213,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>가정 내 대화</t>
+          <t>교육비·사교육비</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -82183,7 +82223,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>자녀와 대화 시간 및 주제 - 6)친구관계</t>
+          <t>교육비 및 사교육 - 2)사교육비_국어, 영어, 수학 등 주요교과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -82193,17 +82233,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2주기 PRQ3_2_6에 1(해당) 코드가 없고 0/결측만 존재 — 결측이 '해당'일 가능성. 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>대화 주제(친구관계)·복수응답 동일</t>
+          <t>사교육비(주요교과)·연속형 동일</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -82215,128 +82255,136 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TR_EFFICACY_08</t>
+          <t>PR_EDU_COST_03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>교사 전문성</t>
+          <t>교육격차·가정배경</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>교사 사기</t>
+          <t>교육비·사교육비</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>교사</t>
+          <t>학부모</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>교사효능감·교사의 사기 - 8)나는 책임감이 높다</t>
+          <t>교육비 및 사교육 - 3)사교육비_영어를 제외한 외국어</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>③ 비교 불가</t>
+          <t>① 연계가능</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>사기 하위척도(8~10번) 평균을 시계열로 쓸 경우 8번 제외 후 2문항 평균으로 재구성 검토</t>
+          <t>사교육비(영어 제외 외국어)·연속형 동일</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>측정방식 상이 — 비교 불가</t>
+          <t>2주기 코딩 이상(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TR_TRAIN_03</t>
+          <t>PR_EDU_COST_04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>교사 전문성</t>
+          <t>교육격차·가정배경</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>교사 연수</t>
+          <t>교육비·사교육비</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>교사</t>
+          <t>학부모</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>교사 연수 항목 및 수강 시간 - 3)자기계발</t>
+          <t>교육비 및 사교육 - 4)사교육비_예체능</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>④ 해당 없음</t>
+          <t>① 연계가능</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>excluded</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1주기 3)자기계발 항목이 2주기에서 삭제됨</t>
+          <t>사교육비(예체능)·연속형 동일</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>한 주기에만 존재</t>
+          <t>2주기 코딩 이상(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ST_COMP_SC_TOT</t>
+          <t>PR_EDU_COST_05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>학생성장</t>
+          <t>교육격차·가정배경</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>역량점수</t>
+          <t>교육비·사교육비</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>학부모</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>사회적 역량 원점수(총점)</t>
+          <t>교육비 및 사교육 - 5)사교육비_기타</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>③ 비교 불가</t>
+          <t>① 연계가능</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -82344,61 +82392,313 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>만점 상이(80 vs 100). 원점수 직접 비교 불가 — 환산점수 사용</t>
+          <t>사교육비(기타)·연속형 동일</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>측정방식 상이 — 비교 불가</t>
+          <t>2주기 코딩 이상(확인 필요)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>PR_TALK_06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>교육격차·가정배경</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>가정 내 대화</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>학부모</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>자녀와 대화 시간 및 주제 - 5)학교생활</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>① 연계가능</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2주기 PRQ3_2_5에 1(해당) 코드가 없고 0/결측만 존재 — 결측이 '해당'일 가능성. 연구원 확인 필요</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>대화 주제(학교생활)·복수응답 동일</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2주기 코딩 이상(확인 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PR_TALK_07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>교육격차·가정배경</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>가정 내 대화</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>학부모</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>자녀와 대화 시간 및 주제 - 6)친구관계</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>① 연계가능</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2주기 PRQ3_2_6에 1(해당) 코드가 없고 0/결측만 존재 — 결측이 '해당'일 가능성. 연구원 확인 필요</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>대화 주제(친구관계)·복수응답 동일</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2주기 코딩 이상(확인 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TR_EFFICACY_08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>교사 전문성</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>교사 사기</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>교사</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>교사효능감·교사의 사기 - 8)나는 책임감이 높다</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>③ 비교 불가</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>사기 하위척도(8~10번) 평균을 시계열로 쓸 경우 8번 제외 후 2문항 평균으로 재구성 검토</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>측정방식 상이 — 비교 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TR_TRAIN_03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>교사 전문성</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>교사 연수</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>교사</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>교사 연수 항목 및 수강 시간 - 3)자기계발</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>④ 해당 없음</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>excluded</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1주기 3)자기계발 항목이 2주기에서 삭제됨</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>한 주기에만 존재</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ST_COMP_SC_TOT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>학생성장</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>역량점수</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>학생</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>사회적 역량 원점수(총점)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>③ 비교 불가</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>만점 상이(80 vs 100). 원점수 직접 비교 불가 — 환산점수 사용</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>측정방식 상이 — 비교 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>ST_COMP_AC_TOT</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>학생성장</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>역량점수</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>학생</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>자율적 역량 원점수(총점)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>③ 비교 불가</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>만점 상이(48 vs 60). 원점수 직접 비교 불가 — 환산점수 사용</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>측정방식 상이 — 비교 불가</t>
         </is>

--- a/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
@@ -11055,7 +11055,7 @@
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>척도 부적합</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -11539,7 +11539,7 @@
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -71696,7 +71696,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>척도 부적합</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -71964,7 +71964,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>

--- a/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
@@ -13208,14 +13208,14 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr"/>
@@ -13318,14 +13318,14 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr"/>
@@ -13428,14 +13428,14 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr"/>
@@ -13538,14 +13538,14 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr"/>
@@ -13648,14 +13648,14 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr"/>
@@ -72897,17 +72897,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>조건부</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr"/>
@@ -72968,17 +72968,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
+          <t>조건부</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
@@ -73039,17 +73039,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
+          <t>조건부</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
@@ -73110,17 +73110,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>조건부</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr"/>
@@ -73181,17 +73181,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
+          <t>조건부</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 전체 평균은 응답 기저가 다르다. 시계열 비교에는 가정이 필요 없는 '지출자평균/지출자중앙값'을 사용할 것. '평균'·'지출참여율'은 2주기 결측=미지출 가정을 전제한다.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
@@ -82045,7 +82045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82151,7 +82151,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PR_EDU_COST_01</t>
+          <t>PR_TALK_06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -82161,7 +82161,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>교육비·사교육비</t>
+          <t>가정 내 대화</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -82171,7 +82171,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>교육비 및 사교육 - 1)학교에 낸 돈(체험활동비, 방과 후 학교 수강료 포함)</t>
+          <t>자녀와 대화 시간 및 주제 - 5)학교생활</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -82181,17 +82181,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>2주기 PRQ3_2_5에 1(해당) 코드가 없고 0/결측만 존재 — 결측이 '해당'일 가능성. 연구원 확인 필요</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>양 주기 모두 이상치 확인 필요(2주기 코드북에 이상치 주의 명시)</t>
+          <t>대화 주제(학교생활)·복수응답 동일</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -82203,7 +82203,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PR_EDU_COST_02</t>
+          <t>PR_TALK_07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -82213,7 +82213,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>교육비·사교육비</t>
+          <t>가정 내 대화</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -82223,7 +82223,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>교육비 및 사교육 - 2)사교육비_국어, 영어, 수학 등 주요교과</t>
+          <t>자녀와 대화 시간 및 주제 - 6)친구관계</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -82233,17 +82233,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
+          <t>2주기 PRQ3_2_6에 1(해당) 코드가 없고 0/결측만 존재 — 결측이 '해당'일 가능성. 연구원 확인 필요</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>사교육비(주요교과)·연속형 동일</t>
+          <t>대화 주제(친구관계)·복수응답 동일</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -82255,136 +82255,128 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PR_EDU_COST_03</t>
+          <t>TR_EFFICACY_08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>교육격차·가정배경</t>
+          <t>교사 전문성</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>교육비·사교육비</t>
+          <t>교사 사기</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>교사</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>교육비 및 사교육 - 3)사교육비_영어를 제외한 외국어</t>
+          <t>교사효능감·교사의 사기 - 8)나는 책임감이 높다</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>① 연계가능</t>
+          <t>③ 비교 불가</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
-        </is>
-      </c>
+          <t>likert</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>사교육비(영어 제외 외국어)·연속형 동일</t>
+          <t>사기 하위척도(8~10번) 평균을 시계열로 쓸 경우 8번 제외 후 2문항 평균으로 재구성 검토</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2주기 코딩 이상(확인 필요)</t>
+          <t>측정방식 상이 — 비교 불가</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PR_EDU_COST_04</t>
+          <t>TR_TRAIN_03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>교육격차·가정배경</t>
+          <t>교사 전문성</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>교육비·사교육비</t>
+          <t>교사 연수</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>교사</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>교육비 및 사교육 - 4)사교육비_예체능</t>
+          <t>교사 연수 항목 및 수강 시간 - 3)자기계발</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>① 연계가능</t>
+          <t>④ 해당 없음</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
-        </is>
-      </c>
+          <t>excluded</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>사교육비(예체능)·연속형 동일</t>
+          <t>1주기 3)자기계발 항목이 2주기에서 삭제됨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2주기 코딩 이상(확인 필요)</t>
+          <t>한 주기에만 존재</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PR_EDU_COST_05</t>
+          <t>ST_COMP_SC_TOT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>교육격차·가정배경</t>
+          <t>학생성장</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>교육비·사교육비</t>
+          <t>역량점수</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>학생</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>교육비 및 사교육 - 5)사교육비_기타</t>
+          <t>사회적 역량 원점수(총점)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>① 연계가능</t>
+          <t>③ 비교 불가</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -82392,313 +82384,61 @@
           <t>continuous</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1주기는 미지출을 0으로 기입, 2주기는 공란 처리 — 응답 기저가 달라 현 시점 시계열 비교 불가. 2주기 결측을 0(미지출)으로 볼지 연구원 확인 필요</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>사교육비(기타)·연속형 동일</t>
+          <t>만점 상이(80 vs 100). 원점수 직접 비교 불가 — 환산점수 사용</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2주기 코딩 이상(확인 필요)</t>
+          <t>측정방식 상이 — 비교 불가</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PR_TALK_06</t>
+          <t>ST_COMP_AC_TOT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>교육격차·가정배경</t>
+          <t>학생성장</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>가정 내 대화</t>
+          <t>역량점수</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>학생</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>자녀와 대화 시간 및 주제 - 5)학교생활</t>
+          <t>자율적 역량 원점수(총점)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>① 연계가능</t>
+          <t>③ 비교 불가</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>binary</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2주기 PRQ3_2_5에 1(해당) 코드가 없고 0/결측만 존재 — 결측이 '해당'일 가능성. 연구원 확인 필요</t>
-        </is>
-      </c>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>대화 주제(학교생활)·복수응답 동일</t>
+          <t>만점 상이(48 vs 60). 원점수 직접 비교 불가 — 환산점수 사용</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
-        <is>
-          <t>2주기 코딩 이상(확인 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PR_TALK_07</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>교육격차·가정배경</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>가정 내 대화</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>학부모</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>자녀와 대화 시간 및 주제 - 6)친구관계</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>① 연계가능</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2주기 PRQ3_2_6에 1(해당) 코드가 없고 0/결측만 존재 — 결측이 '해당'일 가능성. 연구원 확인 필요</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>대화 주제(친구관계)·복수응답 동일</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2주기 코딩 이상(확인 필요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TR_EFFICACY_08</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>교사 전문성</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>교사 사기</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>교사</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>교사효능감·교사의 사기 - 8)나는 책임감이 높다</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>③ 비교 불가</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>사기 하위척도(8~10번) 평균을 시계열로 쓸 경우 8번 제외 후 2문항 평균으로 재구성 검토</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>측정방식 상이 — 비교 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TR_TRAIN_03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>교사 전문성</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>교사 연수</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>교사</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>교사 연수 항목 및 수강 시간 - 3)자기계발</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>④ 해당 없음</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>excluded</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1주기 3)자기계발 항목이 2주기에서 삭제됨</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>한 주기에만 존재</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ST_COMP_SC_TOT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>학생성장</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>역량점수</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>학생</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>사회적 역량 원점수(총점)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>③ 비교 불가</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>만점 상이(80 vs 100). 원점수 직접 비교 불가 — 환산점수 사용</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>측정방식 상이 — 비교 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ST_COMP_AC_TOT</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>학생성장</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>역량점수</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>학생</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>자율적 역량 원점수(총점)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>③ 비교 불가</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>만점 상이(48 vs 60). 원점수 직접 비교 불가 — 환산점수 사용</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>측정방식 상이 — 비교 불가</t>
         </is>

--- a/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
@@ -2552,12 +2552,16 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
@@ -2670,12 +2674,16 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
@@ -2788,12 +2796,16 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -2911,7 +2923,11 @@
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
@@ -3024,12 +3040,16 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -3142,12 +3162,16 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
@@ -3260,12 +3284,16 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -3378,12 +3406,16 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -3501,7 +3533,11 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -3614,12 +3650,16 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -66867,7 +66907,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -66875,7 +66915,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
@@ -66883,19 +66927,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M5" t="n">
         <v>1055</v>
       </c>
       <c r="N5" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O5" t="n">
         <v>4118</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4396</v>
+        <v>1.4749</v>
       </c>
       <c r="Q5" t="n">
         <v>1.4961</v>
@@ -66934,7 +66978,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -66942,7 +66986,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
@@ -66950,19 +66998,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M6" t="n">
         <v>1055</v>
       </c>
       <c r="N6" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O6" t="n">
         <v>4118</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5223</v>
+        <v>1.5615</v>
       </c>
       <c r="Q6" t="n">
         <v>1.6224</v>
@@ -67001,7 +67049,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -67009,7 +67057,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
@@ -67017,19 +67069,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M7" t="n">
         <v>1055</v>
       </c>
       <c r="N7" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O7" t="n">
         <v>4118</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5427</v>
+        <v>1.5777</v>
       </c>
       <c r="Q7" t="n">
         <v>1.7256</v>
@@ -67076,7 +67128,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
@@ -67084,19 +67140,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M8" t="n">
         <v>1055</v>
       </c>
       <c r="N8" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O8" t="n">
         <v>4118</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9645</v>
+        <v>2.0357</v>
       </c>
       <c r="Q8" t="n">
         <v>2.5029</v>
@@ -67135,7 +67191,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -67143,7 +67199,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
@@ -67151,19 +67211,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M9" t="n">
         <v>1055</v>
       </c>
       <c r="N9" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O9" t="n">
         <v>4118</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0343</v>
+        <v>2.0766</v>
       </c>
       <c r="Q9" t="n">
         <v>1.7171</v>
@@ -67202,7 +67262,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -67210,7 +67270,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
@@ -67218,19 +67282,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M10" t="n">
         <v>1055</v>
       </c>
       <c r="N10" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O10" t="n">
         <v>4118</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2125</v>
+        <v>1.2231</v>
       </c>
       <c r="Q10" t="n">
         <v>1.255</v>
@@ -67269,7 +67333,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -67277,7 +67341,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -67285,19 +67353,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M11" t="n">
         <v>1055</v>
       </c>
       <c r="N11" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O11" t="n">
         <v>4118</v>
       </c>
       <c r="P11" t="n">
-        <v>1.2578</v>
+        <v>1.2686</v>
       </c>
       <c r="Q11" t="n">
         <v>1.3167</v>
@@ -67336,7 +67404,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -67344,7 +67412,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
@@ -67352,19 +67424,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M12" t="n">
         <v>1055</v>
       </c>
       <c r="N12" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O12" t="n">
         <v>4118</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4141</v>
+        <v>1.4369</v>
       </c>
       <c r="Q12" t="n">
         <v>1.5918</v>
@@ -67411,7 +67483,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
@@ -67419,19 +67495,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M13" t="n">
         <v>1055</v>
       </c>
       <c r="N13" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O13" t="n">
         <v>4118</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7653</v>
+        <v>1.8147</v>
       </c>
       <c r="Q13" t="n">
         <v>2.2989</v>
@@ -67470,7 +67546,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>조건부</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -67478,7 +67554,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2주기는 사교육 참여자만 응답(분기 오류 추정). 1주기도 사교육 참여자로 한정하여 기저 정렬</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
@@ -67486,19 +67566,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="M14" t="n">
         <v>1055</v>
       </c>
       <c r="N14" t="n">
-        <v>8884</v>
+        <v>7141</v>
       </c>
       <c r="O14" t="n">
         <v>4118</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9967</v>
+        <v>2.0295</v>
       </c>
       <c r="Q14" t="n">
         <v>1.6889</v>

--- a/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/데이터매핑정의서.xlsx
@@ -66728,16 +66728,16 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O2" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7652</v>
+        <v>0.7493333333333334</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7572</v>
+        <v>0.7458666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -66795,16 +66795,16 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O3" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0595</v>
+        <v>0.05683333333333333</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0406</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="4">
@@ -66862,16 +66862,16 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O4" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1862</v>
+        <v>0.1742333333333333</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.167</v>
+        <v>0.1659333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -66927,22 +66927,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M5" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4749</v>
+        <v>1.4677</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4961</v>
+        <v>1.493233333333333</v>
       </c>
     </row>
     <row r="6">
@@ -66998,22 +66998,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M6" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N6" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O6" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5615</v>
+        <v>1.551666666666667</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6224</v>
+        <v>1.612966666666667</v>
       </c>
     </row>
     <row r="7">
@@ -67069,22 +67069,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M7" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N7" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O7" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5777</v>
+        <v>1.576266666666666</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7256</v>
+        <v>1.729433333333333</v>
       </c>
     </row>
     <row r="8">
@@ -67140,22 +67140,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M8" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N8" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O8" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0357</v>
+        <v>1.9982</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5029</v>
+        <v>2.4632</v>
       </c>
     </row>
     <row r="9">
@@ -67211,22 +67211,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M9" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N9" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O9" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0766</v>
+        <v>2.084566666666667</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7171</v>
+        <v>1.704466666666667</v>
       </c>
     </row>
     <row r="10">
@@ -67282,22 +67282,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M10" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N10" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O10" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2231</v>
+        <v>1.2213</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.255</v>
+        <v>1.264333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -67353,22 +67353,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M11" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N11" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O11" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P11" t="n">
-        <v>1.2686</v>
+        <v>1.2625</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.3167</v>
+        <v>1.320066666666667</v>
       </c>
     </row>
     <row r="12">
@@ -67424,22 +67424,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M12" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N12" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O12" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4369</v>
+        <v>1.4357</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.5918</v>
+        <v>1.595966666666667</v>
       </c>
     </row>
     <row r="13">
@@ -67495,22 +67495,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M13" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N13" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O13" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8147</v>
+        <v>1.787433333333333</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2989</v>
+        <v>2.2875</v>
       </c>
     </row>
     <row r="14">
@@ -67566,22 +67566,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1743</v>
+        <v>1162</v>
       </c>
       <c r="M14" t="n">
-        <v>1055</v>
+        <v>703.3333333333334</v>
       </c>
       <c r="N14" t="n">
-        <v>7141</v>
+        <v>4760.666666666667</v>
       </c>
       <c r="O14" t="n">
-        <v>4118</v>
+        <v>2745.333333333333</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0295</v>
+        <v>2.0396</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6889</v>
+        <v>1.678333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -67639,16 +67639,16 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O15" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8727</v>
+        <v>1.866266666666667</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.0037</v>
+        <v>1.990533333333333</v>
       </c>
     </row>
     <row r="16">
@@ -67706,16 +67706,16 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O16" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P16" t="n">
-        <v>1.437</v>
+        <v>1.440066666666667</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8397</v>
+        <v>1.834033333333333</v>
       </c>
     </row>
     <row r="17">
@@ -67773,16 +67773,16 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O17" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0063</v>
+        <v>2.000166666666666</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1724</v>
+        <v>2.156066666666666</v>
       </c>
     </row>
     <row r="18">
@@ -67840,16 +67840,16 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O18" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7396</v>
+        <v>1.743533333333333</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.9704</v>
+        <v>1.962933333333333</v>
       </c>
     </row>
     <row r="19">
@@ -67907,16 +67907,16 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O19" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P19" t="n">
-        <v>2.585</v>
+        <v>2.5891</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.6172</v>
+        <v>2.596366666666666</v>
       </c>
     </row>
     <row r="20">
@@ -67974,16 +67974,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O20" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3341</v>
+        <v>2.332766666666667</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3837</v>
+        <v>2.364166666666667</v>
       </c>
     </row>
     <row r="21">
@@ -68041,16 +68041,16 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O21" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5191</v>
+        <v>2.5153</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5966</v>
+        <v>2.584266666666667</v>
       </c>
     </row>
     <row r="22">
@@ -68108,16 +68108,16 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O22" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4116</v>
+        <v>2.4133</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.502</v>
+        <v>2.498166666666667</v>
       </c>
     </row>
     <row r="23">
@@ -68175,16 +68175,16 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O23" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1398</v>
+        <v>3.128866666666667</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1007</v>
+        <v>3.0955</v>
       </c>
     </row>
     <row r="24">
@@ -68242,16 +68242,16 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O24" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P24" t="n">
-        <v>2.8047</v>
+        <v>2.776066666666667</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8042</v>
+        <v>2.7943</v>
       </c>
     </row>
     <row r="25">
@@ -68309,16 +68309,16 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O25" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P25" t="n">
-        <v>2.9006</v>
+        <v>2.899066666666667</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8848</v>
+        <v>2.8939</v>
       </c>
     </row>
     <row r="26">
@@ -68376,16 +68376,16 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O26" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P26" t="n">
-        <v>2.9588</v>
+        <v>2.950133333333333</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.0186</v>
+        <v>3.004</v>
       </c>
     </row>
     <row r="27">
@@ -68443,16 +68443,16 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O27" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P27" t="n">
-        <v>2.977</v>
+        <v>2.9702</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1315</v>
+        <v>3.118966666666667</v>
       </c>
     </row>
     <row r="28">
@@ -68510,16 +68510,16 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O28" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P28" t="n">
-        <v>2.9587</v>
+        <v>2.958</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.9532</v>
+        <v>2.944133333333333</v>
       </c>
     </row>
     <row r="29">
@@ -68577,16 +68577,16 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O29" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P29" t="n">
-        <v>3.5734</v>
+        <v>3.5674</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5683</v>
+        <v>3.550833333333333</v>
       </c>
     </row>
     <row r="30">
@@ -68644,16 +68644,16 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O30" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P30" t="n">
-        <v>3.0844</v>
+        <v>3.0785</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1342</v>
+        <v>3.121266666666667</v>
       </c>
     </row>
     <row r="31">
@@ -68711,16 +68711,16 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O31" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P31" t="n">
-        <v>2.8949</v>
+        <v>2.8988</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.9981</v>
+        <v>2.986766666666667</v>
       </c>
     </row>
     <row r="32">
@@ -68778,16 +68778,16 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O32" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P32" t="n">
-        <v>3.1986</v>
+        <v>3.2024</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2579</v>
+        <v>3.2658</v>
       </c>
     </row>
     <row r="33">
@@ -68845,16 +68845,16 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O33" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P33" t="n">
-        <v>3.2436</v>
+        <v>3.243133333333333</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3018</v>
+        <v>3.299766666666667</v>
       </c>
     </row>
     <row r="34">
@@ -68912,16 +68912,16 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O34" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P34" t="n">
-        <v>2.9837</v>
+        <v>2.982166666666667</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.0342</v>
+        <v>3.044066666666667</v>
       </c>
     </row>
     <row r="35">
@@ -68979,16 +68979,16 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O35" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P35" t="n">
-        <v>3.3112</v>
+        <v>3.305333333333333</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3313</v>
+        <v>3.337133333333334</v>
       </c>
     </row>
     <row r="36">
@@ -69046,16 +69046,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O36" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P36" t="n">
-        <v>3.6888</v>
+        <v>3.682633333333333</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6797</v>
+        <v>3.680766666666667</v>
       </c>
     </row>
     <row r="37">
@@ -69113,16 +69113,16 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O37" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P37" t="n">
-        <v>3.3018</v>
+        <v>3.3028</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2126</v>
+        <v>3.2311</v>
       </c>
     </row>
     <row r="38">
@@ -69180,16 +69180,16 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O38" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P38" t="n">
-        <v>3.2118</v>
+        <v>3.208866666666667</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.203</v>
+        <v>3.211266666666667</v>
       </c>
     </row>
     <row r="39">
@@ -69247,16 +69247,16 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O39" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P39" t="n">
-        <v>3.5429</v>
+        <v>3.551733333333333</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4493</v>
+        <v>3.461666666666666</v>
       </c>
     </row>
     <row r="40">
@@ -69314,16 +69314,16 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O40" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P40" t="n">
-        <v>3.885</v>
+        <v>3.887566666666667</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.866</v>
+        <v>3.859833333333333</v>
       </c>
     </row>
     <row r="41">
@@ -69381,16 +69381,16 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O41" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P41" t="n">
-        <v>3.6387</v>
+        <v>3.637433333333334</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4786</v>
+        <v>3.4877</v>
       </c>
     </row>
     <row r="42">
@@ -69448,16 +69448,16 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O42" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P42" t="n">
-        <v>3.3745</v>
+        <v>3.37</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3279</v>
+        <v>3.328366666666666</v>
       </c>
     </row>
     <row r="43">
@@ -69515,16 +69515,16 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O43" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P43" t="n">
-        <v>3.7695</v>
+        <v>3.759866666666667</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.8096</v>
+        <v>3.809766666666667</v>
       </c>
     </row>
     <row r="44">
@@ -69582,16 +69582,16 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O44" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P44" t="n">
-        <v>3.1703</v>
+        <v>3.159766666666667</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2333</v>
+        <v>3.242266666666667</v>
       </c>
     </row>
     <row r="45">
@@ -69649,16 +69649,16 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O45" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P45" t="n">
-        <v>3.3721</v>
+        <v>3.365133333333333</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3783</v>
+        <v>3.352666666666666</v>
       </c>
     </row>
     <row r="46">
@@ -69716,16 +69716,16 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O46" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P46" t="n">
-        <v>3.6112</v>
+        <v>3.6133</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.6855</v>
+        <v>3.663633333333333</v>
       </c>
     </row>
     <row r="47">
@@ -69783,16 +69783,16 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O47" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P47" t="n">
-        <v>3.4498</v>
+        <v>3.4545</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.4839</v>
+        <v>3.4718</v>
       </c>
     </row>
     <row r="48">
@@ -69850,16 +69850,16 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O48" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P48" t="n">
-        <v>3.3775</v>
+        <v>3.378666666666666</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4032</v>
+        <v>3.399466666666667</v>
       </c>
     </row>
     <row r="49">
@@ -69917,16 +69917,16 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O49" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P49" t="n">
-        <v>3.804</v>
+        <v>3.802733333333334</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.8635</v>
+        <v>3.871133333333333</v>
       </c>
     </row>
     <row r="50">
@@ -69984,16 +69984,16 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O50" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P50" t="n">
-        <v>3.5834</v>
+        <v>3.5916</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.6147</v>
+        <v>3.626133333333333</v>
       </c>
     </row>
     <row r="51">
@@ -70051,16 +70051,16 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O51" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P51" t="n">
-        <v>3.7331</v>
+        <v>3.740766666666667</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.8011</v>
+        <v>3.811133333333333</v>
       </c>
     </row>
     <row r="52">
@@ -70118,16 +70118,16 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O52" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P52" t="n">
-        <v>3.9726</v>
+        <v>3.969166666666667</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.8347</v>
+        <v>3.835</v>
       </c>
     </row>
     <row r="53">
@@ -70185,16 +70185,16 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O53" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P53" t="n">
-        <v>3.1489</v>
+        <v>3.157366666666667</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2826</v>
+        <v>3.292033333333333</v>
       </c>
     </row>
     <row r="54">
@@ -70252,16 +70252,16 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O54" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P54" t="n">
-        <v>3.3793</v>
+        <v>3.381466666666667</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.4444</v>
+        <v>3.455166666666667</v>
       </c>
     </row>
     <row r="55">
@@ -70319,16 +70319,16 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O55" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P55" t="n">
-        <v>3.6036</v>
+        <v>3.600866666666667</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.728</v>
+        <v>3.744633333333333</v>
       </c>
     </row>
     <row r="56">
@@ -70386,16 +70386,16 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O56" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P56" t="n">
-        <v>3.5009</v>
+        <v>3.500233333333334</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.5853</v>
+        <v>3.604366666666667</v>
       </c>
     </row>
     <row r="57">
@@ -70453,16 +70453,16 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O57" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P57" t="n">
-        <v>3.2042</v>
+        <v>3.214433333333333</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4315</v>
+        <v>3.434866666666667</v>
       </c>
     </row>
     <row r="58">
@@ -70520,16 +70520,16 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O58" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P58" t="n">
-        <v>2.7084</v>
+        <v>2.733633333333334</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.9416</v>
+        <v>2.946866666666667</v>
       </c>
     </row>
     <row r="59">
@@ -70587,16 +70587,16 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O59" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P59" t="n">
-        <v>3.5355</v>
+        <v>3.5411</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.5198</v>
+        <v>3.530233333333333</v>
       </c>
     </row>
     <row r="60">
@@ -70654,16 +70654,16 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O60" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P60" t="n">
-        <v>3.8844</v>
+        <v>3.879466666666667</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.49</v>
+        <v>3.5108</v>
       </c>
     </row>
     <row r="61">
@@ -70721,16 +70721,16 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O61" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P61" t="n">
-        <v>3.5776</v>
+        <v>3.579266666666667</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.5788</v>
+        <v>3.5917</v>
       </c>
     </row>
     <row r="62">
@@ -70788,16 +70788,16 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O62" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P62" t="n">
-        <v>3.7267</v>
+        <v>3.726433333333333</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.7083</v>
+        <v>3.715133333333334</v>
       </c>
     </row>
     <row r="63">
@@ -70855,16 +70855,16 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O63" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P63" t="n">
-        <v>3.5813</v>
+        <v>3.583366666666667</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.6557</v>
+        <v>3.664933333333333</v>
       </c>
     </row>
     <row r="64">
@@ -70922,16 +70922,16 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O64" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P64" t="n">
-        <v>3.2498</v>
+        <v>3.2265</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.388</v>
+        <v>3.373533333333333</v>
       </c>
     </row>
     <row r="65">
@@ -70989,16 +70989,16 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O65" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P65" t="n">
-        <v>2.9871</v>
+        <v>2.968233333333334</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.9751</v>
+        <v>2.985133333333334</v>
       </c>
     </row>
     <row r="66">
@@ -71056,16 +71056,16 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O66" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P66" t="n">
-        <v>3.4806</v>
+        <v>3.460466666666667</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.4442</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="67">
@@ -71123,16 +71123,16 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O67" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P67" t="n">
-        <v>3.6892</v>
+        <v>3.672866666666666</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.7187</v>
+        <v>3.702</v>
       </c>
     </row>
     <row r="68">
@@ -71190,16 +71190,16 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O68" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P68" t="n">
-        <v>3.5966</v>
+        <v>3.583833333333333</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.635</v>
+        <v>3.6199</v>
       </c>
     </row>
     <row r="69">
@@ -71257,16 +71257,16 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O69" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P69" t="n">
-        <v>3.6443</v>
+        <v>3.630966666666667</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.6733</v>
+        <v>3.666566666666667</v>
       </c>
     </row>
     <row r="70">
@@ -71324,16 +71324,16 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O70" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P70" t="n">
-        <v>3.0508</v>
+        <v>3.045733333333333</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.1788</v>
+        <v>3.188333333333333</v>
       </c>
     </row>
     <row r="71">
@@ -71391,16 +71391,16 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O71" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P71" t="n">
-        <v>3.2775</v>
+        <v>3.273633333333333</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3644</v>
+        <v>3.365533333333333</v>
       </c>
     </row>
     <row r="72">
@@ -71458,16 +71458,16 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O72" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P72" t="n">
-        <v>3.6281</v>
+        <v>3.623766666666667</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6619</v>
+        <v>3.644433333333334</v>
       </c>
     </row>
     <row r="73">
@@ -71525,16 +71525,16 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O73" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P73" t="n">
-        <v>3.9605</v>
+        <v>3.9458</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.1506</v>
+        <v>4.146066666666667</v>
       </c>
     </row>
     <row r="74">
@@ -71592,16 +71592,16 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O74" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P74" t="n">
-        <v>3.8641</v>
+        <v>3.847766666666667</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.994</v>
+        <v>3.992666666666667</v>
       </c>
     </row>
     <row r="75">
@@ -71659,16 +71659,16 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O75" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P75" t="n">
-        <v>3.8439</v>
+        <v>3.8323</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.9851</v>
+        <v>3.9809</v>
       </c>
     </row>
     <row r="76">
@@ -71726,16 +71726,16 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O76" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P76" t="n">
-        <v>3.9357</v>
+        <v>3.936233333333333</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.9323</v>
+        <v>3.943366666666666</v>
       </c>
     </row>
     <row r="77">
@@ -71793,16 +71793,16 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O77" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P77" t="n">
-        <v>2.8836</v>
+        <v>2.895233333333334</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.2376</v>
+        <v>3.234866666666667</v>
       </c>
     </row>
     <row r="78">
@@ -71860,16 +71860,16 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O78" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P78" t="n">
-        <v>3.7678</v>
+        <v>3.7637</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.7903</v>
+        <v>3.796333333333333</v>
       </c>
     </row>
     <row r="79">
@@ -71927,16 +71927,16 @@
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O79" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P79" t="n">
-        <v>3.8485</v>
+        <v>3.8464</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.8245</v>
+        <v>3.840666666666667</v>
       </c>
     </row>
     <row r="80">
@@ -71994,16 +71994,16 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O80" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P80" t="n">
-        <v>3.8718</v>
+        <v>3.878</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.8734</v>
+        <v>3.892833333333333</v>
       </c>
     </row>
     <row r="81">
@@ -72061,16 +72061,16 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O81" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P81" t="n">
-        <v>1.9633</v>
+        <v>1.954966666666667</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.2631</v>
+        <v>2.244266666666667</v>
       </c>
     </row>
     <row r="82">
@@ -72128,16 +72128,16 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O82" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P82" t="n">
-        <v>2.5326</v>
+        <v>2.5579</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.8803</v>
+        <v>2.904466666666667</v>
       </c>
     </row>
     <row r="83">
@@ -72195,16 +72195,16 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O83" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P83" t="n">
-        <v>3.9282</v>
+        <v>3.926066666666667</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.9453</v>
+        <v>3.970266666666667</v>
       </c>
     </row>
     <row r="84">
@@ -72262,16 +72262,16 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O84" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P84" t="n">
-        <v>3.4831</v>
+        <v>3.4883</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.4866</v>
+        <v>3.511266666666666</v>
       </c>
     </row>
     <row r="85">
@@ -72329,16 +72329,16 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O85" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P85" t="n">
-        <v>3.4644</v>
+        <v>3.470566666666667</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.4821</v>
+        <v>3.4991</v>
       </c>
     </row>
     <row r="86">
@@ -72396,16 +72396,16 @@
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O86" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P86" t="n">
-        <v>3.2342</v>
+        <v>3.238733333333334</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.3325</v>
+        <v>3.327466666666667</v>
       </c>
     </row>
     <row r="87">
@@ -72463,16 +72463,16 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O87" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P87" t="n">
-        <v>3.5116</v>
+        <v>3.511</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.624</v>
+        <v>3.634533333333334</v>
       </c>
     </row>
     <row r="88">
@@ -72530,16 +72530,16 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O88" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P88" t="n">
-        <v>3.5589</v>
+        <v>3.5756</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.5482</v>
+        <v>3.5878</v>
       </c>
     </row>
     <row r="89">
@@ -72597,16 +72597,16 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O89" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P89" t="n">
-        <v>3.5442</v>
+        <v>3.553233333333333</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.5623</v>
+        <v>3.5912</v>
       </c>
     </row>
     <row r="90">
@@ -72664,16 +72664,16 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O90" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P90" t="n">
-        <v>3.4043</v>
+        <v>3.4198</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.4394</v>
+        <v>3.472233333333334</v>
       </c>
     </row>
     <row r="91">
@@ -72731,16 +72731,16 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O91" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P91" t="n">
-        <v>3.5419</v>
+        <v>3.5484</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.5842</v>
+        <v>3.604533333333334</v>
       </c>
     </row>
     <row r="92">
@@ -72798,16 +72798,16 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O92" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P92" t="n">
-        <v>3.311</v>
+        <v>3.325266666666666</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.7568</v>
+        <v>3.799866666666667</v>
       </c>
     </row>
     <row r="93">
@@ -72865,16 +72865,16 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O93" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P93" t="n">
-        <v>3.4385</v>
+        <v>3.450933333333333</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.5737</v>
+        <v>3.600833333333334</v>
       </c>
     </row>
     <row r="94">
@@ -72932,16 +72932,16 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O94" t="n">
-        <v>5173</v>
+        <v>3448.666666666667</v>
       </c>
       <c r="P94" t="n">
-        <v>3.5053</v>
+        <v>3.511233333333333</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.562</v>
+        <v>3.582066666666667</v>
       </c>
     </row>
     <row r="95">
@@ -73000,19 +73000,19 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>718</v>
+        <v>478.6666666666667</v>
       </c>
       <c r="N95" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O95" t="n">
-        <v>764</v>
+        <v>509.3333333333333</v>
       </c>
       <c r="P95" t="n">
-        <v>0.7814</v>
+        <v>0.7932</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.3988</v>
+        <v>5.9219</v>
       </c>
     </row>
     <row r="96">
@@ -73071,19 +73071,19 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>232</v>
+        <v>154.6666666666667</v>
       </c>
       <c r="N96" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O96" t="n">
-        <v>1250</v>
+        <v>833.3333333333334</v>
       </c>
       <c r="P96" t="n">
-        <v>47.2656</v>
+        <v>44.5016</v>
       </c>
       <c r="Q96" t="n">
-        <v>80.16160000000001</v>
+        <v>77.52249999999999</v>
       </c>
     </row>
     <row r="97">
@@ -73142,19 +73142,19 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1226</v>
+        <v>817.3333333333334</v>
       </c>
       <c r="N97" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O97" t="n">
-        <v>256</v>
+        <v>170.6666666666667</v>
       </c>
       <c r="P97" t="n">
-        <v>1.9539</v>
+        <v>1.840633333333333</v>
       </c>
       <c r="Q97" t="n">
-        <v>7.832</v>
+        <v>7.158666666666666</v>
       </c>
     </row>
     <row r="98">
@@ -73213,19 +73213,19 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>919</v>
+        <v>612.6666666666666</v>
       </c>
       <c r="N98" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O98" t="n">
-        <v>563</v>
+        <v>375.3333333333333</v>
       </c>
       <c r="P98" t="n">
-        <v>6.3025</v>
+        <v>5.991666666666667</v>
       </c>
       <c r="Q98" t="n">
-        <v>29.4938</v>
+        <v>31.6423</v>
       </c>
     </row>
     <row r="99">
@@ -73284,19 +73284,19 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>1171</v>
+        <v>780.6666666666666</v>
       </c>
       <c r="N99" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O99" t="n">
-        <v>311</v>
+        <v>207.3333333333333</v>
       </c>
       <c r="P99" t="n">
-        <v>3.4165</v>
+        <v>3.230733333333333</v>
       </c>
       <c r="Q99" t="n">
-        <v>11.9887</v>
+        <v>11.36903333333333</v>
       </c>
     </row>
     <row r="100">
@@ -73354,16 +73354,16 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O100" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P100" t="n">
-        <v>4.1086</v>
+        <v>4.102766666666667</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.3435</v>
+        <v>4.3038</v>
       </c>
     </row>
     <row r="101">
@@ -73421,16 +73421,16 @@
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O101" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P101" t="n">
-        <v>0.7419</v>
+        <v>0.7339333333333333</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6108</v>
       </c>
     </row>
     <row r="102">
@@ -73488,16 +73488,16 @@
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O102" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P102" t="n">
-        <v>0.3152</v>
+        <v>0.3152333333333333</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.2476</v>
+        <v>0.2543</v>
       </c>
     </row>
     <row r="103">
@@ -73555,16 +73555,16 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O103" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P103" t="n">
-        <v>0.5531</v>
+        <v>0.5568666666666667</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.3313</v>
+        <v>0.3332</v>
       </c>
     </row>
     <row r="104">
@@ -73622,16 +73622,16 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O104" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P104" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7479</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.5655</v>
+        <v>0.5684666666666667</v>
       </c>
     </row>
     <row r="105">
@@ -73690,16 +73690,16 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>1113</v>
+        <v>742</v>
       </c>
       <c r="N105" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O105" t="n">
-        <v>369</v>
+        <v>246</v>
       </c>
       <c r="P105" t="n">
-        <v>0.7863</v>
+        <v>0.7842333333333333</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -73761,16 +73761,16 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>961</v>
+        <v>640.6666666666666</v>
       </c>
       <c r="N106" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O106" t="n">
-        <v>521</v>
+        <v>347.3333333333333</v>
       </c>
       <c r="P106" t="n">
-        <v>0.7781</v>
+        <v>0.7791</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -73831,16 +73831,16 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O107" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P107" t="n">
-        <v>1.29</v>
+        <v>1.290133333333333</v>
       </c>
       <c r="Q107" t="n">
-        <v>1.2692</v>
+        <v>1.252033333333333</v>
       </c>
     </row>
     <row r="108">
@@ -73898,16 +73898,16 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O108" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P108" t="n">
-        <v>1.8517</v>
+        <v>1.841533333333333</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.7699</v>
+        <v>1.750566666666667</v>
       </c>
     </row>
     <row r="109">
@@ -73965,16 +73965,16 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O109" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P109" t="n">
-        <v>1.8904</v>
+        <v>1.883766666666667</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.8077</v>
+        <v>1.791566666666667</v>
       </c>
     </row>
     <row r="110">
@@ -74032,16 +74032,16 @@
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O110" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P110" t="n">
-        <v>1.3608</v>
+        <v>1.3784</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.3401</v>
+        <v>1.350766666666667</v>
       </c>
     </row>
     <row r="111">
@@ -74099,16 +74099,16 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O111" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P111" t="n">
-        <v>1.5679</v>
+        <v>1.5761</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.5061</v>
+        <v>1.524666666666667</v>
       </c>
     </row>
     <row r="112">
@@ -74166,16 +74166,16 @@
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O112" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P112" t="n">
-        <v>1.7924</v>
+        <v>1.784766666666667</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.4676</v>
+        <v>1.472066666666667</v>
       </c>
     </row>
     <row r="113">
@@ -74233,16 +74233,16 @@
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O113" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P113" t="n">
-        <v>1.4766</v>
+        <v>1.483633333333333</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.3043</v>
+        <v>1.314266666666667</v>
       </c>
     </row>
     <row r="114">
@@ -74300,16 +74300,16 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O114" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P114" t="n">
-        <v>1.5232</v>
+        <v>1.533766666666667</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.3623</v>
+        <v>1.368166666666667</v>
       </c>
     </row>
     <row r="115">
@@ -74367,16 +74367,16 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O115" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P115" t="n">
-        <v>1.3921</v>
+        <v>1.408466666666667</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.2571</v>
+        <v>1.2613</v>
       </c>
     </row>
     <row r="116">
@@ -74432,22 +74432,22 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1725</v>
+        <v>1150</v>
       </c>
       <c r="M116" t="n">
-        <v>399</v>
+        <v>266</v>
       </c>
       <c r="N116" t="n">
-        <v>4223</v>
+        <v>2815.333333333333</v>
       </c>
       <c r="O116" t="n">
-        <v>1083</v>
+        <v>722</v>
       </c>
       <c r="P116" t="n">
-        <v>3.5091</v>
+        <v>3.501133333333333</v>
       </c>
       <c r="Q116" t="n">
-        <v>4.0536</v>
+        <v>4.0461</v>
       </c>
     </row>
     <row r="117">
@@ -74503,22 +74503,22 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>5066</v>
+        <v>3377.333333333333</v>
       </c>
       <c r="M117" t="n">
-        <v>1141</v>
+        <v>760.6666666666666</v>
       </c>
       <c r="N117" t="n">
-        <v>882</v>
+        <v>588</v>
       </c>
       <c r="O117" t="n">
-        <v>341</v>
+        <v>227.3333333333333</v>
       </c>
       <c r="P117" t="n">
-        <v>3.4127</v>
+        <v>3.4297</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.9238</v>
+        <v>3.932666666666667</v>
       </c>
     </row>
     <row r="118">
@@ -74574,22 +74574,22 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>5296</v>
+        <v>3530.666666666667</v>
       </c>
       <c r="M118" t="n">
-        <v>1197</v>
+        <v>798</v>
       </c>
       <c r="N118" t="n">
-        <v>652</v>
+        <v>434.6666666666667</v>
       </c>
       <c r="O118" t="n">
-        <v>285</v>
+        <v>190</v>
       </c>
       <c r="P118" t="n">
-        <v>3.4325</v>
+        <v>3.446033333333334</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.9439</v>
+        <v>3.967533333333333</v>
       </c>
     </row>
     <row r="119">
@@ -74645,22 +74645,22 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2146</v>
+        <v>1430.666666666667</v>
       </c>
       <c r="M119" t="n">
-        <v>504</v>
+        <v>336</v>
       </c>
       <c r="N119" t="n">
-        <v>3802</v>
+        <v>2534.666666666667</v>
       </c>
       <c r="O119" t="n">
-        <v>978</v>
+        <v>652</v>
       </c>
       <c r="P119" t="n">
-        <v>3.455</v>
+        <v>3.449233333333333</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.9458</v>
+        <v>3.9437</v>
       </c>
     </row>
     <row r="120">
@@ -74716,22 +74716,22 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3378</v>
+        <v>2252</v>
       </c>
       <c r="M120" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="N120" t="n">
-        <v>2570</v>
+        <v>1713.333333333333</v>
       </c>
       <c r="O120" t="n">
-        <v>732</v>
+        <v>488</v>
       </c>
       <c r="P120" t="n">
-        <v>3.2899</v>
+        <v>3.294733333333333</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.7828</v>
+        <v>3.804966666666667</v>
       </c>
     </row>
     <row r="121">
@@ -74787,22 +74787,22 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>4713</v>
+        <v>3142</v>
       </c>
       <c r="M121" t="n">
-        <v>693</v>
+        <v>462</v>
       </c>
       <c r="N121" t="n">
-        <v>1235</v>
+        <v>823.3333333333334</v>
       </c>
       <c r="O121" t="n">
-        <v>789</v>
+        <v>526</v>
       </c>
       <c r="P121" t="n">
-        <v>3.4988</v>
+        <v>3.513766666666667</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.0684</v>
+        <v>4.052266666666667</v>
       </c>
     </row>
     <row r="122">
@@ -74858,22 +74858,22 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2835</v>
+        <v>1890</v>
       </c>
       <c r="M122" t="n">
-        <v>451</v>
+        <v>300.6666666666667</v>
       </c>
       <c r="N122" t="n">
-        <v>3113</v>
+        <v>2075.333333333333</v>
       </c>
       <c r="O122" t="n">
-        <v>1031</v>
+        <v>687.3333333333334</v>
       </c>
       <c r="P122" t="n">
-        <v>3.2936</v>
+        <v>3.300866666666666</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.8099</v>
+        <v>3.796633333333334</v>
       </c>
     </row>
     <row r="123">
@@ -74929,22 +74929,22 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3112</v>
+        <v>2074.666666666667</v>
       </c>
       <c r="M123" t="n">
-        <v>537</v>
+        <v>358</v>
       </c>
       <c r="N123" t="n">
-        <v>2836</v>
+        <v>1890.666666666667</v>
       </c>
       <c r="O123" t="n">
-        <v>945</v>
+        <v>630</v>
       </c>
       <c r="P123" t="n">
-        <v>3.299</v>
+        <v>3.2958</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.6889</v>
+        <v>3.678566666666667</v>
       </c>
     </row>
     <row r="124">
@@ -75000,22 +75000,22 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2332</v>
+        <v>1554.666666666667</v>
       </c>
       <c r="M124" t="n">
-        <v>381</v>
+        <v>254</v>
       </c>
       <c r="N124" t="n">
-        <v>3616</v>
+        <v>2410.666666666667</v>
       </c>
       <c r="O124" t="n">
-        <v>1101</v>
+        <v>734</v>
       </c>
       <c r="P124" t="n">
-        <v>3.3308</v>
+        <v>3.328733333333334</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.7593</v>
+        <v>3.730633333333333</v>
       </c>
     </row>
     <row r="125">
@@ -75073,16 +75073,16 @@
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O125" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P125" t="n">
-        <v>3.2875</v>
+        <v>3.2619</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.3023</v>
+        <v>3.265333333333333</v>
       </c>
     </row>
     <row r="126">
@@ -75140,16 +75140,16 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O126" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P126" t="n">
-        <v>1.1696</v>
+        <v>1.167966666666667</v>
       </c>
       <c r="Q126" t="n">
-        <v>1.525</v>
+        <v>1.534566666666667</v>
       </c>
     </row>
     <row r="127">
@@ -75201,22 +75201,22 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>4828</v>
+        <v>3218.666666666667</v>
       </c>
       <c r="M127" t="n">
-        <v>868</v>
+        <v>578.6666666666666</v>
       </c>
       <c r="N127" t="n">
-        <v>1120</v>
+        <v>746.6666666666666</v>
       </c>
       <c r="O127" t="n">
-        <v>614</v>
+        <v>409.3333333333333</v>
       </c>
       <c r="P127" t="n">
-        <v>2.9161</v>
+        <v>2.925366666666667</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.0423</v>
+        <v>3.043</v>
       </c>
     </row>
     <row r="128">
@@ -75268,22 +75268,22 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>4828</v>
+        <v>3218.666666666667</v>
       </c>
       <c r="M128" t="n">
-        <v>868</v>
+        <v>578.6666666666666</v>
       </c>
       <c r="N128" t="n">
-        <v>1120</v>
+        <v>746.6666666666666</v>
       </c>
       <c r="O128" t="n">
-        <v>614</v>
+        <v>409.3333333333333</v>
       </c>
       <c r="P128" t="n">
-        <v>3.1259</v>
+        <v>3.1394</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.2101</v>
+        <v>3.1906</v>
       </c>
     </row>
     <row r="129">
@@ -75335,22 +75335,22 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>4828</v>
+        <v>3218.666666666667</v>
       </c>
       <c r="M129" t="n">
-        <v>868</v>
+        <v>578.6666666666666</v>
       </c>
       <c r="N129" t="n">
-        <v>1120</v>
+        <v>746.6666666666666</v>
       </c>
       <c r="O129" t="n">
-        <v>614</v>
+        <v>409.3333333333333</v>
       </c>
       <c r="P129" t="n">
-        <v>3.075</v>
+        <v>3.089833333333333</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.145</v>
+        <v>3.1424</v>
       </c>
     </row>
     <row r="130">
@@ -75408,16 +75408,16 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O130" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P130" t="n">
-        <v>4.059</v>
+        <v>4.065700000000001</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.9953</v>
+        <v>4.0046</v>
       </c>
     </row>
     <row r="131">
@@ -75475,16 +75475,16 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O131" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P131" t="n">
-        <v>2.2608</v>
+        <v>2.2696</v>
       </c>
       <c r="Q131" t="n">
-        <v>2.6437</v>
+        <v>2.634266666666667</v>
       </c>
     </row>
     <row r="132">
@@ -75542,16 +75542,16 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O132" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P132" t="n">
-        <v>3.8248</v>
+        <v>3.834166666666667</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.7638</v>
+        <v>3.7632</v>
       </c>
     </row>
     <row r="133">
@@ -75609,16 +75609,16 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O133" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P133" t="n">
-        <v>3.9578</v>
+        <v>3.9603</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.9757</v>
+        <v>4.002266666666666</v>
       </c>
     </row>
     <row r="134">
@@ -75676,16 +75676,16 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O134" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P134" t="n">
-        <v>1.9702</v>
+        <v>1.971233333333333</v>
       </c>
       <c r="Q134" t="n">
-        <v>2.1269</v>
+        <v>2.090566666666667</v>
       </c>
     </row>
     <row r="135">
@@ -75743,16 +75743,16 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O135" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P135" t="n">
-        <v>2.8974</v>
+        <v>2.908533333333333</v>
       </c>
       <c r="Q135" t="n">
-        <v>2.9413</v>
+        <v>2.979933333333333</v>
       </c>
     </row>
     <row r="136">
@@ -75810,16 +75810,16 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O136" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P136" t="n">
-        <v>3.6298</v>
+        <v>3.634266666666667</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.6916</v>
+        <v>3.7029</v>
       </c>
     </row>
     <row r="137">
@@ -75877,16 +75877,16 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O137" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P137" t="n">
-        <v>3.4511</v>
+        <v>3.462766666666667</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.5209</v>
+        <v>3.544666666666667</v>
       </c>
     </row>
     <row r="138">
@@ -75944,16 +75944,16 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O138" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P138" t="n">
-        <v>3.2229</v>
+        <v>3.236766666666667</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.3077</v>
+        <v>3.333933333333333</v>
       </c>
     </row>
     <row r="139">
@@ -76011,16 +76011,16 @@
         <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O139" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P139" t="n">
-        <v>3.4185</v>
+        <v>3.431133333333333</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.4906</v>
+        <v>3.5102</v>
       </c>
     </row>
     <row r="140">
@@ -76078,16 +76078,16 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O140" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P140" t="n">
-        <v>3.4296</v>
+        <v>3.4306</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.504</v>
+        <v>3.532233333333334</v>
       </c>
     </row>
     <row r="141">
@@ -76145,16 +76145,16 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O141" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P141" t="n">
-        <v>3.6439</v>
+        <v>3.653566666666666</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.753</v>
+        <v>3.775466666666667</v>
       </c>
     </row>
     <row r="142">
@@ -76212,16 +76212,16 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O142" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P142" t="n">
-        <v>3.2485</v>
+        <v>3.2655</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.3354</v>
+        <v>3.354366666666667</v>
       </c>
     </row>
     <row r="143">
@@ -76279,16 +76279,16 @@
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O143" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P143" t="n">
-        <v>3.3117</v>
+        <v>3.3219</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.3671</v>
+        <v>3.3818</v>
       </c>
     </row>
     <row r="144">
@@ -76346,16 +76346,16 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O144" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P144" t="n">
-        <v>3.4016</v>
+        <v>3.406733333333333</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.4818</v>
+        <v>3.508766666666666</v>
       </c>
     </row>
     <row r="145">
@@ -76413,16 +76413,16 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O145" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P145" t="n">
-        <v>3.5358</v>
+        <v>3.534166666666666</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.587</v>
+        <v>3.5995</v>
       </c>
     </row>
     <row r="146">
@@ -76480,16 +76480,16 @@
         <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5948</v>
+        <v>3965.333333333333</v>
       </c>
       <c r="O146" t="n">
-        <v>1482</v>
+        <v>988</v>
       </c>
       <c r="P146" t="n">
-        <v>3.7549</v>
+        <v>3.7546</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.8043</v>
+        <v>3.8153</v>
       </c>
     </row>
     <row r="147">
@@ -76547,16 +76547,16 @@
         <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O147" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P147" t="n">
-        <v>4.1301</v>
+        <v>4.131766666666667</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.9471</v>
+        <v>3.954233333333333</v>
       </c>
     </row>
     <row r="148">
@@ -76614,16 +76614,16 @@
         <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O148" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P148" t="n">
-        <v>4.2114</v>
+        <v>4.2156</v>
       </c>
       <c r="Q148" t="n">
-        <v>4.1279</v>
+        <v>4.137066666666667</v>
       </c>
     </row>
     <row r="149">
@@ -76681,16 +76681,16 @@
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O149" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P149" t="n">
-        <v>4.3592</v>
+        <v>4.3658</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.245</v>
+        <v>4.250066666666666</v>
       </c>
     </row>
     <row r="150">
@@ -76748,16 +76748,16 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O150" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P150" t="n">
-        <v>4.0291</v>
+        <v>4.031666666666666</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.0032</v>
+        <v>4.008933333333333</v>
       </c>
     </row>
     <row r="151">
@@ -76815,16 +76815,16 @@
         <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O151" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P151" t="n">
-        <v>3.884</v>
+        <v>3.884233333333333</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.8307</v>
+        <v>3.8448</v>
       </c>
     </row>
     <row r="152">
@@ -76882,16 +76882,16 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O152" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P152" t="n">
-        <v>4.0663</v>
+        <v>4.072133333333333</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.98</v>
+        <v>3.997733333333333</v>
       </c>
     </row>
     <row r="153">
@@ -76949,16 +76949,16 @@
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O153" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P153" t="n">
-        <v>4.0366</v>
+        <v>4.035333333333333</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.7293</v>
+        <v>3.740933333333333</v>
       </c>
     </row>
     <row r="154">
@@ -77016,16 +77016,16 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O154" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P154" t="n">
-        <v>4.0455</v>
+        <v>4.049133333333333</v>
       </c>
       <c r="Q154" t="n">
-        <v>4.4561</v>
+        <v>4.467933333333334</v>
       </c>
     </row>
     <row r="155">
@@ -77083,16 +77083,16 @@
         <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O155" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P155" t="n">
-        <v>4.2384</v>
+        <v>4.239266666666667</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.3739</v>
+        <v>4.3914</v>
       </c>
     </row>
     <row r="156">
@@ -77150,16 +77150,16 @@
         <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O156" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P156" t="n">
-        <v>4.2619</v>
+        <v>4.27</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.1457</v>
+        <v>4.167866666666666</v>
       </c>
     </row>
     <row r="157">
@@ -77217,16 +77217,16 @@
         <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O157" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P157" t="n">
-        <v>2.9069</v>
+        <v>2.878333333333333</v>
       </c>
       <c r="Q157" t="n">
-        <v>2.9696</v>
+        <v>2.9327</v>
       </c>
     </row>
     <row r="158">
@@ -77284,16 +77284,16 @@
         <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O158" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P158" t="n">
-        <v>2.9405</v>
+        <v>2.937133333333334</v>
       </c>
       <c r="Q158" t="n">
-        <v>2.7039</v>
+        <v>2.7045</v>
       </c>
     </row>
     <row r="159">
@@ -77351,16 +77351,16 @@
         <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O159" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P159" t="n">
-        <v>3.5787</v>
+        <v>3.5729</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.4682</v>
+        <v>3.4518</v>
       </c>
     </row>
     <row r="160">
@@ -77418,16 +77418,16 @@
         <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O160" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P160" t="n">
-        <v>3.4768</v>
+        <v>3.476066666666667</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.7289</v>
+        <v>3.7125</v>
       </c>
     </row>
     <row r="161">
@@ -77485,16 +77485,16 @@
         <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O161" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P161" t="n">
-        <v>2.6387</v>
+        <v>2.5984</v>
       </c>
       <c r="Q161" t="n">
-        <v>2.1971</v>
+        <v>2.1688</v>
       </c>
     </row>
     <row r="162">
@@ -77552,16 +77552,16 @@
         <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O162" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P162" t="n">
-        <v>2.4951</v>
+        <v>2.459533333333333</v>
       </c>
       <c r="Q162" t="n">
-        <v>2.3371</v>
+        <v>2.326933333333333</v>
       </c>
     </row>
     <row r="163">
@@ -77619,16 +77619,16 @@
         <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O163" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P163" t="n">
-        <v>3.1565</v>
+        <v>3.138366666666666</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.155</v>
+        <v>3.1592</v>
       </c>
     </row>
     <row r="164">
@@ -77686,16 +77686,16 @@
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O164" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P164" t="n">
-        <v>4.7529</v>
+        <v>4.692766666666667</v>
       </c>
       <c r="Q164" t="n">
-        <v>4.6364</v>
+        <v>4.618766666666667</v>
       </c>
     </row>
     <row r="165">
@@ -77753,16 +77753,16 @@
         <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O165" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P165" t="n">
-        <v>2.1663</v>
+        <v>2.217566666666666</v>
       </c>
       <c r="Q165" t="n">
-        <v>2.0339</v>
+        <v>2.084466666666667</v>
       </c>
     </row>
     <row r="166">
@@ -77820,16 +77820,16 @@
         <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O166" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P166" t="n">
-        <v>5.5045</v>
+        <v>5.447233333333333</v>
       </c>
       <c r="Q166" t="n">
-        <v>5.3593</v>
+        <v>5.356933333333333</v>
       </c>
     </row>
     <row r="167">
@@ -77887,16 +77887,16 @@
         <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O167" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P167" t="n">
-        <v>2.3191</v>
+        <v>2.3589</v>
       </c>
       <c r="Q167" t="n">
-        <v>2.2371</v>
+        <v>2.2578</v>
       </c>
     </row>
     <row r="168">
@@ -77954,16 +77954,16 @@
         <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O168" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P168" t="n">
-        <v>2.9</v>
+        <v>2.898666666666667</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.2579</v>
+        <v>3.2938</v>
       </c>
     </row>
     <row r="169">
@@ -78021,16 +78021,16 @@
         <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O169" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P169" t="n">
-        <v>2.318</v>
+        <v>2.334966666666667</v>
       </c>
       <c r="Q169" t="n">
-        <v>2.8646</v>
+        <v>2.886033333333333</v>
       </c>
     </row>
     <row r="170">
@@ -78086,11 +78086,11 @@
       </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="n">
-        <v>2.6205</v>
+        <v>2.666133333333333</v>
       </c>
       <c r="Q170" t="inlineStr"/>
     </row>
@@ -78149,16 +78149,16 @@
         <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O171" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P171" t="n">
-        <v>2.0551</v>
+        <v>2.0841</v>
       </c>
       <c r="Q171" t="n">
-        <v>2.1493</v>
+        <v>2.156966666666667</v>
       </c>
     </row>
     <row r="172">
@@ -78216,16 +78216,16 @@
         <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O172" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P172" t="n">
-        <v>2.0133</v>
+        <v>2.0521</v>
       </c>
       <c r="Q172" t="n">
-        <v>2.2314</v>
+        <v>2.252533333333333</v>
       </c>
     </row>
     <row r="173">
@@ -78283,16 +78283,16 @@
         <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O173" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P173" t="n">
-        <v>2.1274</v>
+        <v>2.148566666666667</v>
       </c>
       <c r="Q173" t="n">
-        <v>2.1879</v>
+        <v>2.195133333333333</v>
       </c>
     </row>
     <row r="174">
@@ -78350,16 +78350,16 @@
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O174" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P174" t="n">
-        <v>2.5146</v>
+        <v>2.542</v>
       </c>
       <c r="Q174" t="n">
-        <v>2.4871</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="175">
@@ -78417,16 +78417,16 @@
         <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O175" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P175" t="n">
-        <v>3.6992</v>
+        <v>3.700133333333333</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.5236</v>
+        <v>3.534066666666666</v>
       </c>
     </row>
     <row r="176">
@@ -78484,16 +78484,16 @@
         <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O176" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P176" t="n">
-        <v>4.2904</v>
+        <v>4.2871</v>
       </c>
       <c r="Q176" t="n">
-        <v>4.2339</v>
+        <v>4.240333333333333</v>
       </c>
     </row>
     <row r="177">
@@ -78551,16 +78551,16 @@
         <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O177" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P177" t="n">
-        <v>3.7448</v>
+        <v>3.748666666666667</v>
       </c>
       <c r="Q177" t="n">
-        <v>3.8629</v>
+        <v>3.8757</v>
       </c>
     </row>
     <row r="178">
@@ -78618,16 +78618,16 @@
         <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O178" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P178" t="n">
-        <v>4.2012</v>
+        <v>4.187166666666667</v>
       </c>
       <c r="Q178" t="n">
-        <v>4.0996</v>
+        <v>4.101533333333333</v>
       </c>
     </row>
     <row r="179">
@@ -78685,16 +78685,16 @@
         <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O179" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P179" t="n">
-        <v>4.1345</v>
+        <v>4.1224</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.9971</v>
+        <v>3.998366666666667</v>
       </c>
     </row>
     <row r="180">
@@ -78752,16 +78752,16 @@
         <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O180" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P180" t="n">
-        <v>4.1852</v>
+        <v>4.178933333333333</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.9982</v>
+        <v>4.009233333333333</v>
       </c>
     </row>
     <row r="181">
@@ -78819,16 +78819,16 @@
         <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O181" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P181" t="n">
-        <v>4.1087</v>
+        <v>4.112766666666666</v>
       </c>
       <c r="Q181" t="n">
-        <v>4.0293</v>
+        <v>4.060433333333333</v>
       </c>
     </row>
     <row r="182">
@@ -78886,16 +78886,16 @@
         <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O182" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P182" t="n">
-        <v>4.0759</v>
+        <v>4.078566666666666</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.9743</v>
+        <v>4.022666666666667</v>
       </c>
     </row>
     <row r="183">
@@ -78953,16 +78953,16 @@
         <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O183" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P183" t="n">
-        <v>4.0451</v>
+        <v>4.051566666666667</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.8836</v>
+        <v>3.9398</v>
       </c>
     </row>
     <row r="184">
@@ -79020,16 +79020,16 @@
         <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O184" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P184" t="n">
-        <v>4.0143</v>
+        <v>4.027766666666667</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.8364</v>
+        <v>3.8983</v>
       </c>
     </row>
     <row r="185">
@@ -79087,16 +79087,16 @@
         <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O185" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P185" t="n">
-        <v>4.3914</v>
+        <v>4.401066666666667</v>
       </c>
       <c r="Q185" t="n">
-        <v>4.05</v>
+        <v>4.0758</v>
       </c>
     </row>
     <row r="186">
@@ -79154,16 +79154,16 @@
         <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O186" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P186" t="n">
-        <v>4.4421</v>
+        <v>4.425333333333334</v>
       </c>
       <c r="Q186" t="n">
-        <v>4.2639</v>
+        <v>4.262066666666667</v>
       </c>
     </row>
     <row r="187">
@@ -79221,16 +79221,16 @@
         <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O187" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P187" t="n">
-        <v>4.4203</v>
+        <v>4.407033333333334</v>
       </c>
       <c r="Q187" t="n">
-        <v>4.1811</v>
+        <v>4.184566666666666</v>
       </c>
     </row>
     <row r="188">
@@ -79288,16 +79288,16 @@
         <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O188" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P188" t="n">
-        <v>4.4363</v>
+        <v>4.436866666666667</v>
       </c>
       <c r="Q188" t="n">
-        <v>4.1518</v>
+        <v>4.1905</v>
       </c>
     </row>
     <row r="189">
@@ -79355,16 +79355,16 @@
         <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O189" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P189" t="n">
-        <v>3.2976</v>
+        <v>3.3316</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.3636</v>
+        <v>3.4285</v>
       </c>
     </row>
     <row r="190">
@@ -79422,16 +79422,16 @@
         <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O190" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P190" t="n">
-        <v>4.2802</v>
+        <v>4.282699999999999</v>
       </c>
       <c r="Q190" t="n">
-        <v>4.1093</v>
+        <v>4.0946</v>
       </c>
     </row>
     <row r="191">
@@ -79489,16 +79489,16 @@
         <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O191" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P191" t="n">
-        <v>4.1964</v>
+        <v>4.190733333333333</v>
       </c>
       <c r="Q191" t="n">
-        <v>4.0293</v>
+        <v>4.032766666666666</v>
       </c>
     </row>
     <row r="192">
@@ -79556,16 +79556,16 @@
         <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O192" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P192" t="n">
-        <v>3.8846</v>
+        <v>3.904233333333333</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.8093</v>
+        <v>3.830433333333333</v>
       </c>
     </row>
     <row r="193">
@@ -79623,16 +79623,16 @@
         <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O193" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P193" t="n">
-        <v>3.7533</v>
+        <v>3.760466666666666</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.7554</v>
+        <v>3.802</v>
       </c>
     </row>
     <row r="194">
@@ -79690,16 +79690,16 @@
         <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O194" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P194" t="n">
-        <v>4.1299</v>
+        <v>4.136066666666667</v>
       </c>
       <c r="Q194" t="n">
-        <v>4.1721</v>
+        <v>4.201533333333333</v>
       </c>
     </row>
     <row r="195">
@@ -79757,16 +79757,16 @@
         <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O195" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P195" t="n">
-        <v>4.1659</v>
+        <v>4.1687</v>
       </c>
       <c r="Q195" t="n">
-        <v>4.2107</v>
+        <v>4.244233333333333</v>
       </c>
     </row>
     <row r="196">
@@ -79824,16 +79824,16 @@
         <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O196" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P196" t="n">
-        <v>3.9493</v>
+        <v>3.959633333333333</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.9132</v>
+        <v>3.973333333333333</v>
       </c>
     </row>
     <row r="197">
@@ -79891,16 +79891,16 @@
         <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O197" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P197" t="n">
-        <v>3.6535</v>
+        <v>3.667966666666667</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.5329</v>
+        <v>3.572666666666667</v>
       </c>
     </row>
     <row r="198">
@@ -79958,16 +79958,16 @@
         <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O198" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P198" t="n">
-        <v>3.816</v>
+        <v>3.8341</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.7493</v>
+        <v>3.796</v>
       </c>
     </row>
     <row r="199">
@@ -80025,16 +80025,16 @@
         <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O199" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P199" t="n">
-        <v>3.7934</v>
+        <v>3.8031</v>
       </c>
       <c r="Q199" t="n">
-        <v>3.8404</v>
+        <v>3.868066666666666</v>
       </c>
     </row>
     <row r="200">
@@ -80092,16 +80092,16 @@
         <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O200" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P200" t="n">
-        <v>4.2079</v>
+        <v>4.198900000000001</v>
       </c>
       <c r="Q200" t="n">
-        <v>3.9925</v>
+        <v>4.033666666666666</v>
       </c>
     </row>
     <row r="201">
@@ -80159,16 +80159,16 @@
         <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O201" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P201" t="n">
-        <v>4.079</v>
+        <v>4.062566666666666</v>
       </c>
       <c r="Q201" t="n">
-        <v>3.9364</v>
+        <v>3.955333333333333</v>
       </c>
     </row>
     <row r="202">
@@ -80226,16 +80226,16 @@
         <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O202" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P202" t="n">
-        <v>4.0426</v>
+        <v>4.031366666666667</v>
       </c>
       <c r="Q202" t="n">
-        <v>3.8718</v>
+        <v>3.9014</v>
       </c>
     </row>
     <row r="203">
@@ -80293,16 +80293,16 @@
         <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O203" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P203" t="n">
-        <v>4.0114</v>
+        <v>3.9976</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.8925</v>
+        <v>3.9248</v>
       </c>
     </row>
     <row r="204">
@@ -80360,16 +80360,16 @@
         <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O204" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P204" t="n">
-        <v>3.7726</v>
+        <v>3.7776</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.7282</v>
+        <v>3.761733333333333</v>
       </c>
     </row>
     <row r="205">
@@ -80427,16 +80427,16 @@
         <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O205" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P205" t="n">
-        <v>3.9408</v>
+        <v>3.9446</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.8786</v>
+        <v>3.922033333333334</v>
       </c>
     </row>
     <row r="206">
@@ -80494,16 +80494,16 @@
         <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O206" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P206" t="n">
-        <v>3.7707</v>
+        <v>3.779166666666667</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.6171</v>
+        <v>3.6864</v>
       </c>
     </row>
     <row r="207">
@@ -80561,16 +80561,16 @@
         <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O207" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P207" t="n">
-        <v>3.8096</v>
+        <v>3.8234</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.6821</v>
+        <v>3.743633333333333</v>
       </c>
     </row>
     <row r="208">
@@ -80628,16 +80628,16 @@
         <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O208" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P208" t="n">
-        <v>3.9484</v>
+        <v>3.951466666666667</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.8889</v>
+        <v>3.929166666666667</v>
       </c>
     </row>
     <row r="209">
@@ -80695,16 +80695,16 @@
         <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O209" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P209" t="n">
-        <v>3.7051</v>
+        <v>3.719</v>
       </c>
       <c r="Q209" t="n">
-        <v>3.5675</v>
+        <v>3.6179</v>
       </c>
     </row>
     <row r="210">
@@ -80762,16 +80762,16 @@
         <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O210" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P210" t="n">
-        <v>3.9946</v>
+        <v>4.010333333333334</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.86</v>
+        <v>3.9002</v>
       </c>
     </row>
     <row r="211">
@@ -80829,16 +80829,16 @@
         <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O211" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P211" t="n">
-        <v>3.8757</v>
+        <v>3.894866666666667</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.7586</v>
+        <v>3.8064</v>
       </c>
     </row>
     <row r="212">
@@ -80896,16 +80896,16 @@
         <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O212" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P212" t="n">
-        <v>3.8927</v>
+        <v>3.913533333333334</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.8089</v>
+        <v>3.8628</v>
       </c>
     </row>
     <row r="213">
@@ -80963,16 +80963,16 @@
         <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O213" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P213" t="n">
-        <v>3.8416</v>
+        <v>3.8627</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.7661</v>
+        <v>3.818966666666667</v>
       </c>
     </row>
     <row r="214">
@@ -81030,16 +81030,16 @@
         <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O214" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P214" t="n">
-        <v>3.7782</v>
+        <v>3.7947</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.5832</v>
+        <v>3.6381</v>
       </c>
     </row>
     <row r="215">
@@ -81097,16 +81097,16 @@
         <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O215" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P215" t="n">
-        <v>4.1079</v>
+        <v>4.122866666666667</v>
       </c>
       <c r="Q215" t="n">
-        <v>3.9171</v>
+        <v>3.9657</v>
       </c>
     </row>
     <row r="216">
@@ -81164,16 +81164,16 @@
         <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O216" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P216" t="n">
-        <v>3.8441</v>
+        <v>3.864566666666667</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.6043</v>
+        <v>3.651733333333333</v>
       </c>
     </row>
     <row r="217">
@@ -81231,16 +81231,16 @@
         <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O217" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P217" t="n">
-        <v>3.6412</v>
+        <v>3.6781</v>
       </c>
       <c r="Q217" t="n">
-        <v>3.2621</v>
+        <v>3.3271</v>
       </c>
     </row>
     <row r="218">
@@ -81298,16 +81298,16 @@
         <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O218" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P218" t="n">
-        <v>3.7156</v>
+        <v>3.733</v>
       </c>
       <c r="Q218" t="n">
-        <v>3.4282</v>
+        <v>3.500566666666666</v>
       </c>
     </row>
     <row r="219">
@@ -81365,16 +81365,16 @@
         <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O219" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P219" t="n">
-        <v>3.8273</v>
+        <v>3.840366666666667</v>
       </c>
       <c r="Q219" t="n">
-        <v>3.5986</v>
+        <v>3.6626</v>
       </c>
     </row>
     <row r="220">
@@ -81432,16 +81432,16 @@
         <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O220" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P220" t="n">
-        <v>3.9493</v>
+        <v>3.9648</v>
       </c>
       <c r="Q220" t="n">
-        <v>3.7821</v>
+        <v>3.8389</v>
       </c>
     </row>
     <row r="221">
@@ -81499,16 +81499,16 @@
         <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O221" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P221" t="n">
-        <v>3.8372</v>
+        <v>3.8378</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.7907</v>
+        <v>3.835733333333334</v>
       </c>
     </row>
     <row r="222">
@@ -81566,16 +81566,16 @@
         <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O222" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P222" t="n">
-        <v>3.8244</v>
+        <v>3.830766666666667</v>
       </c>
       <c r="Q222" t="n">
-        <v>3.7071</v>
+        <v>3.755633333333333</v>
       </c>
     </row>
     <row r="223">
@@ -81633,16 +81633,16 @@
         <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O223" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P223" t="n">
-        <v>3.953</v>
+        <v>3.950733333333333</v>
       </c>
       <c r="Q223" t="n">
-        <v>3.9054</v>
+        <v>3.935833333333334</v>
       </c>
     </row>
     <row r="224">
@@ -81700,16 +81700,16 @@
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>5189</v>
+        <v>3459.333333333333</v>
       </c>
       <c r="O224" t="n">
-        <v>2800</v>
+        <v>1866.666666666667</v>
       </c>
       <c r="P224" t="n">
-        <v>3.9125</v>
+        <v>3.914733333333333</v>
       </c>
       <c r="Q224" t="n">
-        <v>3.8246</v>
+        <v>3.866433333333333</v>
       </c>
     </row>
     <row r="225">
@@ -81764,19 +81764,19 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>484</v>
+        <v>322.6666666666667</v>
       </c>
       <c r="N225" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O225" t="n">
-        <v>4689</v>
+        <v>3126</v>
       </c>
       <c r="P225" t="n">
-        <v>56.4048</v>
+        <v>56.26843333333333</v>
       </c>
       <c r="Q225" t="n">
-        <v>59.1304</v>
+        <v>58.17496666666667</v>
       </c>
     </row>
     <row r="226">
@@ -81831,19 +81831,19 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>484</v>
+        <v>322.6666666666667</v>
       </c>
       <c r="N226" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O226" t="n">
-        <v>4689</v>
+        <v>3126</v>
       </c>
       <c r="P226" t="n">
-        <v>65.81100000000001</v>
+        <v>65.7546</v>
       </c>
       <c r="Q226" t="n">
-        <v>68.87479999999999</v>
+        <v>68.95893333333333</v>
       </c>
     </row>
     <row r="227">
@@ -81898,19 +81898,19 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>484</v>
+        <v>322.6666666666667</v>
       </c>
       <c r="N227" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O227" t="n">
-        <v>4689</v>
+        <v>3126</v>
       </c>
       <c r="P227" t="n">
-        <v>70.24379999999999</v>
+        <v>70.18903333333333</v>
       </c>
       <c r="Q227" t="n">
-        <v>73.0424</v>
+        <v>72.82653333333333</v>
       </c>
     </row>
     <row r="228">
@@ -81965,19 +81965,19 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>484</v>
+        <v>322.6666666666667</v>
       </c>
       <c r="N228" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O228" t="n">
-        <v>4689</v>
+        <v>3126</v>
       </c>
       <c r="P228" t="n">
-        <v>13.5371</v>
+        <v>13.5044</v>
       </c>
       <c r="Q228" t="n">
-        <v>14.1913</v>
+        <v>13.962</v>
       </c>
     </row>
     <row r="229">
@@ -82032,19 +82032,19 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>484</v>
+        <v>322.6666666666667</v>
       </c>
       <c r="N229" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O229" t="n">
-        <v>4689</v>
+        <v>3126</v>
       </c>
       <c r="P229" t="n">
-        <v>52.6488</v>
+        <v>52.6037</v>
       </c>
       <c r="Q229" t="n">
-        <v>75.0998</v>
+        <v>75.16713333333333</v>
       </c>
     </row>
     <row r="230">
@@ -82099,19 +82099,19 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>484</v>
+        <v>322.6666666666667</v>
       </c>
       <c r="N230" t="n">
-        <v>8884</v>
+        <v>5922.666666666667</v>
       </c>
       <c r="O230" t="n">
-        <v>4689</v>
+        <v>3126</v>
       </c>
       <c r="P230" t="n">
-        <v>33.717</v>
+        <v>33.69073333333333</v>
       </c>
       <c r="Q230" t="n">
-        <v>47.0604</v>
+        <v>46.95673333333334</v>
       </c>
     </row>
   </sheetData>
